--- a/reports/benchmark_all_systems.xlsx
+++ b/reports/benchmark_all_systems.xlsx
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A perfect marker marks every answer (the upper limit)</t>
+          <t>The answer key used as the marker (the upper limit)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Verdict-only pass with the exact-match oracle</t>
+          <t>Verdict-only pass with the exact-match oracle; no second model is loaded</t>
         </is>
       </c>
       <c r="D8" t="n">
